--- a/ai.xlsx
+++ b/ai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\box\github\a4a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81669B3D-F5DC-4BA7-97F9-1E046A510425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151ECAC1-D276-4290-AEA1-8D657DCE15CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-9640" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,13 +30,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -92,9 +92,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>502204</xdr:colOff>
+      <xdr:colOff>508554</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>13011</xdr:rowOff>
+      <xdr:rowOff>16186</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -123,6 +123,67 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70EF909-0F05-A4B9-C63E-5E821318B5D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="685800" y="5248275"/>
+          <a:ext cx="7000875" cy="8029575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -394,7 +455,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
